--- a/data/trans_orig/P70A_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P70A_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si dichos problemas de salud fueron causados por su trabajo en 2023</t>
+          <t>Población según si su ausencia en el trabajo por motivos de salud, fue debido a problemas de salud causados por su trabajo en 2023 (tasa de respuesta: 94,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28217</t>
+          <t>28366</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42462</t>
+          <t>42946</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29361</t>
+          <t>28312</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37065</t>
+          <t>37226</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60466</t>
+          <t>60392</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77298</t>
+          <t>77541</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>83,12%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3136</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16542</t>
+          <t>16383</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10222</t>
+          <t>10715</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8839</t>
+          <t>8620</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23747</t>
+          <t>23483</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>12996</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5818</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4315</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15695</t>
+          <t>16251</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42016</t>
+          <t>42101</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>59796</t>
+          <t>59161</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38531</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50114</t>
+          <t>50488</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>85309</t>
+          <t>85845</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>106220</t>
+          <t>107106</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,92%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8241</t>
+          <t>9020</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25605</t>
+          <t>25116</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14987</t>
+          <t>14583</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15841</t>
+          <t>15937</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>36663</t>
+          <t>35087</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9629</t>
+          <t>9564</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14134</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19224</t>
+          <t>18976</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28493</t>
+          <t>28707</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12555</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21366</t>
+          <t>21379</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>35197</t>
+          <t>35050</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>48223</t>
+          <t>47902</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,28%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>846</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>7973</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7413</t>
+          <t>7363</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11571</t>
+          <t>12122</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10328</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2592</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>10852</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17290</t>
+          <t>17614</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32341</t>
+          <t>32953</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47304</t>
+          <t>47666</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28256</t>
+          <t>28080</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36047</t>
+          <t>36261</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64840</t>
+          <t>63683</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80711</t>
+          <t>81079</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,31%</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,62 +2246,62 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>956</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1312</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>4694</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>956</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>5244</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18659</t>
+          <t>17949</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>4195</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12200</t>
+          <t>12376</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>11178</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26945</t>
+          <t>28527</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>30,72%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8686</t>
+          <t>8837</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6125</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9421</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16972</t>
+          <t>16775</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22319</t>
+          <t>22326</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,56%</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>416</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3749</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>838</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,62 +2815,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>913</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>723</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>4418</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>3,87%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>913</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>4269</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22081</t>
+          <t>22212</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31686</t>
+          <t>31719</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14856</t>
+          <t>15111</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21642</t>
+          <t>21627</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>40233</t>
+          <t>40415</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>51741</t>
+          <t>51204</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>82,79%</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7952</t>
+          <t>7664</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10610</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13418</t>
+          <t>13410</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>464</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5294</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>15305</t>
+          <t>15523</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>52593</t>
+          <t>53527</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>70018</t>
+          <t>69887</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>71079</t>
+          <t>72608</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>89005</t>
+          <t>89122</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>132575</t>
+          <t>132112</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>155314</t>
+          <t>155574</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,66%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18356</t>
+          <t>17370</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14847</t>
+          <t>14301</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12028</t>
+          <t>11745</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>27737</t>
+          <t>27787</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>20001</t>
+          <t>19706</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10666</t>
+          <t>10547</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>26829</t>
+          <t>25062</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,47 +3742,47 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
+          <t>9,85%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>23,41%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>27648</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>18979</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>38239</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>14,51%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
           <t>9,96%</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>25,06%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>27648</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>19168</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>38251</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>10,06%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>210359</t>
+          <t>210567</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>294675</t>
+          <t>295299</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>43624</t>
+          <t>42956</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>55660</t>
+          <t>54967</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>263807</t>
+          <t>266176</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>354867</t>
+          <t>354884</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>32843</t>
+          <t>34434</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2933</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11147</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>40182</t>
+          <t>40289</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>496</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>60105</t>
+          <t>54854</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4069</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>13975</t>
+          <t>14588</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>61742</t>
+          <t>58841</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>466632</t>
+          <t>467555</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>606059</t>
+          <t>602534</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>271397</t>
+          <t>272838</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>301046</t>
+          <t>300493</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>759965</t>
+          <t>758757</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>921924</t>
+          <t>939866</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>16767</t>
+          <t>16845</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>83324</t>
+          <t>82460</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>30027</t>
+          <t>29604</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>49106</t>
+          <t>49495</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>38175</t>
+          <t>32106</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>119360</t>
+          <t>119541</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>14829</t>
+          <t>16730</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>94187</t>
+          <t>93105</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>37210</t>
+          <t>37404</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>61315</t>
+          <t>60292</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>48195</t>
+          <t>43622</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>140240</t>
+          <t>141980</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70A_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P70A_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>36319</t>
+          <t>33376</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28366</t>
+          <t>26896</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42946</t>
+          <t>38826</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>33966</t>
+          <t>34229</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28312</t>
+          <t>29800</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37226</t>
+          <t>37574</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>70285</t>
+          <t>67605</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60392</t>
+          <t>59879</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77541</t>
+          <t>74498</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,1%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8285</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>3843</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16383</t>
+          <t>14555</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5938</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10715</t>
+          <t>9767</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>14222</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8620</t>
+          <t>8634</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23483</t>
+          <t>21200</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6525</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12996</t>
+          <t>11755</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2257</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>558</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>8782</t>
+          <t>7936</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16251</t>
+          <t>13986</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51129</t>
+          <t>47057</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51129</t>
+          <t>47057</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51129</t>
+          <t>47057</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42161</t>
+          <t>42588</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42161</t>
+          <t>42588</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42161</t>
+          <t>42588</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>93290</t>
+          <t>89645</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93290</t>
+          <t>89645</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93290</t>
+          <t>89645</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>51813</t>
+          <t>53642</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42101</t>
+          <t>43797</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>59161</t>
+          <t>60618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>44955</t>
+          <t>45941</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>39880</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50488</t>
+          <t>51351</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>96768</t>
+          <t>99583</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>85845</t>
+          <t>88106</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>107106</t>
+          <t>109210</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,06%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15918</t>
+          <t>15620</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9020</t>
+          <t>9248</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25116</t>
+          <t>24933</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8757</t>
+          <t>8604</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14583</t>
+          <t>14197</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>24675</t>
+          <t>24225</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15937</t>
+          <t>15275</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>35087</t>
+          <t>33997</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9564</t>
+          <t>9739</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7724</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3540</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15016</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>70517</t>
+          <t>72025</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70517</t>
+          <t>72025</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70517</t>
+          <t>72025</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58651</t>
+          <t>59464</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58651</t>
+          <t>59464</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>58651</t>
+          <t>59464</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>129168</t>
+          <t>131489</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129168</t>
+          <t>131489</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>129168</t>
+          <t>131489</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24677</t>
+          <t>24101</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18976</t>
+          <t>18244</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28707</t>
+          <t>27857</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17483</t>
+          <t>17491</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>12859</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21379</t>
+          <t>21356</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>42160</t>
+          <t>41592</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>35050</t>
+          <t>34686</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47902</t>
+          <t>47876</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>80,14%</t>
         </is>
       </c>
     </row>
@@ -1750,17 +1750,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>850</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>7725</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7363</t>
+          <t>7367</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7199</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>3718</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12122</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>10650</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5744</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10852</t>
+          <t>10932</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>11063</t>
+          <t>10991</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17614</t>
+          <t>17316</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,99%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33464</t>
+          <t>32834</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33464</t>
+          <t>32834</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>33464</t>
+          <t>32834</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26958</t>
+          <t>26906</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26958</t>
+          <t>26906</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26958</t>
+          <t>26906</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>60422</t>
+          <t>59740</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>60422</t>
+          <t>59740</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>60422</t>
+          <t>59740</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>41099</t>
+          <t>48997</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32953</t>
+          <t>39302</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47666</t>
+          <t>55761</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>32860</t>
+          <t>40184</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28080</t>
+          <t>34455</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36261</t>
+          <t>43546</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>73959</t>
+          <t>89181</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63683</t>
+          <t>78555</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81079</t>
+          <t>96478</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>88,17%</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>928</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>928</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>5835</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10352</t>
+          <t>10986</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17949</t>
+          <t>20703</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>8334</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12376</t>
+          <t>14063</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>17948</t>
+          <t>19319</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11178</t>
+          <t>12213</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>28527</t>
+          <t>29766</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>52407</t>
+          <t>60911</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52407</t>
+          <t>60911</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52407</t>
+          <t>60911</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>40456</t>
+          <t>48518</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40456</t>
+          <t>48518</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40456</t>
+          <t>48518</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>92863</t>
+          <t>109429</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92863</t>
+          <t>109429</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>92863</t>
+          <t>109429</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,27 +2549,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12143</t>
+          <t>13977</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8837</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13741</t>
+          <t>15717</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>9860</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>7650</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9454</t>
+          <t>11148</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>23836</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16775</t>
+          <t>20095</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22326</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>734</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2672,12 +2672,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>452</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>892</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2785,12 +2785,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2855,12 +2855,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>4854</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>13741</t>
+          <t>15717</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13741</t>
+          <t>15717</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13741</t>
+          <t>15717</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>9870</t>
+          <t>11600</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9870</t>
+          <t>11600</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9870</t>
+          <t>11600</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>23611</t>
+          <t>27317</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>23611</t>
+          <t>27317</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23611</t>
+          <t>27317</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>27456</t>
+          <t>27428</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22212</t>
+          <t>22272</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31719</t>
+          <t>31708</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>18964</t>
+          <t>19314</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15111</t>
+          <t>15572</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21627</t>
+          <t>22077</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>46420</t>
+          <t>46742</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>40415</t>
+          <t>40611</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>51204</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>84,39%</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7664</t>
+          <t>7652</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>5806</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>9796</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>7926</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13410</t>
+          <t>12612</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1695</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>474</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>4547</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>9621</t>
+          <t>9356</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>15523</t>
+          <t>14368</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>23,22%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>37025</t>
+          <t>36682</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>37025</t>
+          <t>36682</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>37025</t>
+          <t>36682</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>24822</t>
+          <t>25201</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>24822</t>
+          <t>25201</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>24822</t>
+          <t>25201</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>61847</t>
+          <t>61883</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>61847</t>
+          <t>61883</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>61847</t>
+          <t>61883</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>62475</t>
+          <t>75236</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>53527</t>
+          <t>64011</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>69887</t>
+          <t>84308</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>81763</t>
+          <t>94667</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>72608</t>
+          <t>84585</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>89122</t>
+          <t>102189</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>144239</t>
+          <t>169903</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>132112</t>
+          <t>156908</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>155574</t>
+          <t>182849</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>82,04%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>10166</t>
+          <t>12455</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17370</t>
+          <t>20237</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>8465</t>
+          <t>9896</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14301</t>
+          <t>16271</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>18631</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11745</t>
+          <t>13698</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>27787</t>
+          <t>31877</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>10807</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19706</t>
+          <t>22960</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>17300</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10547</t>
+          <t>11244</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25062</t>
+          <t>26636</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>27648</t>
+          <t>30616</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>18979</t>
+          <t>20915</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>38239</t>
+          <t>42268</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>83448</t>
+          <t>101007</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>83448</t>
+          <t>101007</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>83448</t>
+          <t>101007</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>107069</t>
+          <t>121863</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>107069</t>
+          <t>121863</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>107069</t>
+          <t>121863</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>190518</t>
+          <t>222870</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>190518</t>
+          <t>222870</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>190518</t>
+          <t>222870</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>283547</t>
+          <t>44799</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>210567</t>
+          <t>36495</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>295299</t>
+          <t>50964</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>49885</t>
+          <t>55167</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>42956</t>
+          <t>47383</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>54967</t>
+          <t>61662</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>333432</t>
+          <t>99966</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>266176</t>
+          <t>89340</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>354884</t>
+          <t>109782</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>82,72%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>5470</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>34434</t>
+          <t>12063</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>6324</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>14341</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>11198</t>
+          <t>13750</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>8250</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>40289</t>
+          <t>21963</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>8376</t>
+          <t>9340</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>54854</t>
+          <t>16940</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>9664</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>4478</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14588</t>
+          <t>16558</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>16855</t>
+          <t>19004</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>11200</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>58841</t>
+          <t>29006</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>296797</t>
+          <t>59609</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>296797</t>
+          <t>59609</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>296797</t>
+          <t>59609</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>64688</t>
+          <t>73110</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>64688</t>
+          <t>73110</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>64688</t>
+          <t>73110</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>361485</t>
+          <t>132720</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>361485</t>
+          <t>132720</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>361485</t>
+          <t>132720</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4373,32 +4373,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>539529</t>
+          <t>321554</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>467555</t>
+          <t>302575</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>602534</t>
+          <t>339997</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,32 +4408,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>288086</t>
+          <t>316853</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>272838</t>
+          <t>301184</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>300493</t>
+          <t>332072</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,32 +4443,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>827615</t>
+          <t>638408</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>758757</t>
+          <t>612366</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>939866</t>
+          <t>662070</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>79,28%</t>
         </is>
       </c>
     </row>
@@ -4486,32 +4486,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>45996</t>
+          <t>48163</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>16845</t>
+          <t>34965</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>82460</t>
+          <t>63737</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>39038</t>
+          <t>42612</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>29604</t>
+          <t>34185</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>49495</t>
+          <t>56310</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>85034</t>
+          <t>90775</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>32106</t>
+          <t>73301</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>119541</t>
+          <t>107677</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -4599,32 +4599,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>53004</t>
+          <t>56123</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>16730</t>
+          <t>41392</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>93105</t>
+          <t>71549</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4634,32 +4634,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>47551</t>
+          <t>49786</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>37404</t>
+          <t>37426</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>60292</t>
+          <t>62491</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,32 +4669,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>100556</t>
+          <t>105910</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>43622</t>
+          <t>88747</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>141980</t>
+          <t>127695</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -4712,17 +4712,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>638529</t>
+          <t>425841</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>638529</t>
+          <t>425841</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>638529</t>
+          <t>425841</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>374675</t>
+          <t>409251</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>374675</t>
+          <t>409251</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>374675</t>
+          <t>409251</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1013204</t>
+          <t>835092</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1013204</t>
+          <t>835092</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1013204</t>
+          <t>835092</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
